--- a/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
@@ -2231,13 +2231,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.86</v>
+        <v>-2.85</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>-3.09</v>
@@ -2306,10 +2306,10 @@
         <v>-3.31</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-3.46</v>
+        <v>-3.45</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-3.6</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="7">
@@ -2319,19 +2319,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-1.32</v>
+        <v>-1.31</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-1.66</v>
+        <v>-1.65</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-1.98</v>
+        <v>-1.97</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>-2.18</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-2.39</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="8">
@@ -2353,7 +2353,7 @@
         <v>-0.91</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>-1.18</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="9">
@@ -2366,13 +2366,13 @@
         <v>1.76</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0.7</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>0.04</v>
@@ -2391,7 +2391,7 @@
         <v>2.65</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>1.64</v>
@@ -2404,6 +2404,175 @@
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>The crux in observable units. Both inputs are observable rather than matters of opinion: the first prints daily on a listed futures contract, the second can be read against the sovereign's own borrowing cost. A reader who believes urea holds above US$540 for a decade, or that Egyptian equity risk clears below its sovereign, is reading a different cell rather than disagreeing with the arithmetic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>THE CONTESTED CONSTRUCTIONS — one component moved, model re-run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Choice made</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>The alternative</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>EGP/share</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Against the published</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Country risk priced off the sovereign's credit rating</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Priced off the sovereign's traded default swap instead, which is the narrower of the two spreads</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>-0.3787001056554872</v>
+      </c>
+      <c r="D17" s="11">
+        <f>C17--1.2979590362377038</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>A cost of capital that glides from its spot build to a terminal rate made from its own long-run components</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>One flat spot rate applied to every explicit year and to the perpetuity</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>-1.987476572573648</v>
+      </c>
+      <c r="D18" s="11">
+        <f>C18--1.2979590362377038</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Terminal growth at the central bank's medium-term inflation target</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Two percentage points below it, which is negative real maintenance growth</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>-1.320722068827815</v>
+      </c>
+      <c r="D19" s="11">
+        <f>C19--1.2979590362377038</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Beta from the five-year weekly regression of the share against its own local index</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>The Dimson sum-beta from the same regression, which corrects for co-movement booked late because the share does not trade every session</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>-0.6727564234154667</v>
+      </c>
+      <c r="D20" s="11">
+        <f>C20--1.2979590362377038</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Gas at the realised price the company's own loss disclosure implies</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>The contract formula price in the operating agreement, which is higher</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>-3.086219360288026</v>
+      </c>
+      <c r="D21" s="11">
+        <f>C21--1.2979590362377038</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>The new complex earning at half its derived nameplate in the terminal year</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Seventy per cent, which is what a well-run nitrate line achieves</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>-1.14947084159815</v>
+      </c>
+      <c r="D22" s="11">
+        <f>C22--1.2979590362377038</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Maintenance capital expenditure at three per cent of revenue</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Two per cent, nearer the company's own pre-project observed spend</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>-1.142517849292182</v>
+      </c>
+      <c r="D23" s="11">
+        <f>C23--1.2979590362377038</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Each row is a complete re-run of the model through the same case machinery with one component moved and everything else held. Column C is pasted class 3 and DOES NOT REDRAW; column D is a formula against the published answer so the gap can never drift from the values beside it.</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3276,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.0997886629296782</v>
+        <v>0.09982039444544266</v>
       </c>
     </row>
     <row r="26">
@@ -3452,7 +3621,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>-1.303062066566377</v>
+        <v>-1.297959036237704</v>
       </c>
     </row>
     <row r="24">
@@ -3462,7 +3631,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>2.193914440338019</v>
+        <v>2.199017470666693</v>
       </c>
     </row>
     <row r="25">
@@ -3482,7 +3651,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>6.913273765720695</v>
+        <v>6.918193137103221</v>
       </c>
     </row>
     <row r="27">
@@ -3492,7 +3661,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>3.776277848735929</v>
+        <v>3.776252679840041</v>
       </c>
     </row>
     <row r="29">
@@ -4586,7 +4755,7 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>2145.758056818956</v>
+        <v>2141.977268521675</v>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
@@ -7947,7 +8116,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>14638.955</v>
+        <v>14639.005</v>
       </c>
     </row>
     <row r="40">
@@ -8380,7 +8549,7 @@
         <v>772.634</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>890.591</v>
+        <v>895.849</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>890.591</v>

--- a/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
@@ -2231,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>-0.3787001056554872</v>
+        <v>0.1358918966344949</v>
       </c>
       <c r="D17" s="11">
-        <f>C17--1.2979590362377038</f>
+        <f>C17--0.7910702774432968</f>
         <v/>
       </c>
     </row>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>-1.987476572573648</v>
+        <v>-1.481156639241684</v>
       </c>
       <c r="D18" s="11">
-        <f>C18--1.2979590362377038</f>
+        <f>C18--0.7910702774432968</f>
         <v/>
       </c>
     </row>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>-1.320722068827815</v>
+        <v>-0.8138333100334084</v>
       </c>
       <c r="D19" s="11">
-        <f>C19--1.2979590362377038</f>
+        <f>C19--0.7910702774432968</f>
         <v/>
       </c>
     </row>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>-0.6727564234154667</v>
+        <v>-0.1534648537287934</v>
       </c>
       <c r="D20" s="11">
-        <f>C20--1.2979590362377038</f>
+        <f>C20--0.7910702774432968</f>
         <v/>
       </c>
     </row>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>-3.086219360288026</v>
+        <v>-2.579330601493619</v>
       </c>
       <c r="D21" s="11">
-        <f>C21--1.2979590362377038</f>
+        <f>C21--0.7910702774432968</f>
         <v/>
       </c>
     </row>
@@ -2543,34 +2543,72 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>-1.14947084159815</v>
+        <v>-0.6425820828037434</v>
       </c>
       <c r="D22" s="11">
-        <f>C22--1.2979590362377038</f>
+        <f>C22--0.7910702774432968</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Maintenance capital expenditure at three per cent of revenue</t>
+          <t>Maintenance capital expenditure at the company's own observed pre-project rate of 1.12% of revenue</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Two per cent, nearer the company's own pre-project observed spend</t>
+          <t>Replacement-rate maintenance: gross fixed assets at the disclosed 3.95% machinery depreciation rate, or 6.11% of revenue</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>-1.142517849292182</v>
+        <v>-1.566590242157883</v>
       </c>
       <c r="D23" s="11">
-        <f>C23--1.2979590362377038</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="39" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+        <f>C23--0.7910702774432968</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Terminal reinvestment of 38.9% of operating profit after tax, from growth over an 18% return on capital</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>23.3%, from a 30% return on capital — the rate a newly completed plant earns on incremental capital while it is still filling</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>-0.2216206875244034</v>
+      </c>
+      <c r="D24" s="11">
+        <f>C24--0.7910702774432968</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Project spending anchored on the observed run rate: the nine-month actual extended to a full year</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>The faster profile the first issue of this study used, opening at EGP 3,000m</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>-1.00506105644039</v>
+      </c>
+      <c r="D25" s="11">
+        <f>C25--0.7910702774432968</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="39" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Each row is a complete re-run of the model through the same case machinery with one component moved and everything else held. Column C is pasted class 3 and DOES NOT REDRAW; column D is a formula against the published answer so the gap can never drift from the values beside it.</t>
         </is>
@@ -3276,7 +3314,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.09982039444544266</v>
+        <v>0.10075665145649</v>
       </c>
     </row>
     <row r="26">
@@ -3621,7 +3659,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>-1.297959036237704</v>
+        <v>-0.7910702774432968</v>
       </c>
     </row>
     <row r="24">
@@ -3631,7 +3669,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>2.199017470666693</v>
+        <v>2.491915450464006</v>
       </c>
     </row>
     <row r="25">
@@ -5626,7 +5664,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="24" customHeight="1">
+    <row r="108" ht="48" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2026/27</t>
@@ -5638,15 +5676,15 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>3000</v>
+        <v>2598.8</v>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Project spending path against the bank-approved cost and the observed pace: construction in progress moved from EGP 3,790m to EGP 5,654m over nine months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="24" customHeight="1">
+          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="48" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2027/28</t>
@@ -5658,15 +5696,15 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Project spending path against the bank-approved cost and the observed pace: construction in progress moved from EGP 3,790m to EGP 5,654m over nine months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="24" customHeight="1">
+          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="48" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2028/29</t>
@@ -5678,15 +5716,15 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Project spending path against the bank-approved cost and the observed pace: construction in progress moved from EGP 3,790m to EGP 5,654m over nine months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="24" customHeight="1">
+          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="48" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2029/30</t>
@@ -5698,15 +5736,15 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Project spending path against the bank-approved cost and the observed pace: construction in progress moved from EGP 3,790m to EGP 5,654m over nine months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="24" customHeight="1">
+          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="48" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2030/31</t>
@@ -5718,15 +5756,15 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>2000</v>
+        <v>2489.4</v>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Project spending path against the bank-approved cost and the observed pace: construction in progress moved from EGP 3,790m to EGP 5,654m over nine months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="36" customHeight="1">
+          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="72" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure</t>
@@ -5738,11 +5776,11 @@
         </is>
       </c>
       <c r="C113" s="15" t="n">
-        <v>0.03</v>
+        <v>0.01115699027054101</v>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Maintenance capital expenditure as a share of revenue. The pre-project observed run of EGP 42.5-81m was abnormally low on a newly built plant; 3.0% is the mature-plant standard. No guidance exists, so this is sensitised.</t>
+          <t>Maintenance capital expenditure as a share of revenue, RE-ANCHORED 9 August 2026 on the company's OWN pre-project cash-flow statements: EGP 123.3m spent across FY2021/22 and FY2022/23 on EGP 11,052.9m of revenue. The first issue of this study used a 3.0% mature-plant standard instead, which is 2.7 times what this company has ever spent to keep its plant running, and which no disclosure supports. The replacement-rate framing (gross fixed assets at the disclosed 3.95% machinery rate, 6.11% of revenue) is carried as the published alternative and as the downside case.</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8113,7 @@
         <v/>
       </c>
       <c r="D36" s="14">
-        <f>SUM(B17:F17)+7684.478911</f>
+        <f>SUM(B17:F17)+7259.369324</f>
         <v/>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
@@ -1225,14 +1225,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1506,6 +1506,274 @@
       <c r="F14" s="24">
         <f>'DCF'!F14</f>
         <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>CAPITAL EXPENDITURE RECORD — WHAT THE COMPANY ACTUALLY SPENDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Capital expenditure paid (EGP m)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (EGP m)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Of revenue</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>What it was</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>FY2021/22</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>80.847245</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>4440.701</v>
+      </c>
+      <c r="D22" s="8">
+        <f>B22/C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Before the project</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>FY2022/23</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>42.470154</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>6612.226</v>
+      </c>
+      <c r="D23" s="8">
+        <f>B23/C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Before the project</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>FY2023/24</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n">
+        <v>2396.608259</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>6532.126</v>
+      </c>
+      <c r="D24" s="8">
+        <f>B24/C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>The build begins</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>FY2024/25</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>1545.053761</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>8602.606</v>
+      </c>
+      <c r="D25" s="8">
+        <f>B25/C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>9M FY2025/26</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="n">
+        <v>1949.134461</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>7314.933</v>
+      </c>
+      <c r="D26" s="8">
+        <f>B26/C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Nine months actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Pre-project maintenance rate, the two clean years pooled</t>
+        </is>
+      </c>
+      <c r="D28" s="15">
+        <f>(B22+B23)/(C22+C23)</f>
+        <v/>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>THE MAINTENANCE DRIVER. Assumptions reads this cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Replacement-rate framing, the published alternative</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>17022.493</v>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="D29" s="8">
+        <f>B29*C29/B5</f>
+        <v/>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Gross fixed assets at the disclosed machinery rate, over first-forecast-year revenue. NOT used in the valuation — the downside case, published beside the central and never averaged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Full-year project spend at the observed run rate</t>
+        </is>
+      </c>
+      <c r="B30" s="26">
+        <f>B26*4/3</f>
+        <v/>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>THE PROJECT PATH'S FIRST YEAR. Assumptions reads this cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Rate when the facility was signed, 25 June 2025</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>EGP per US dollar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Approved cost of the programme (EGP m)</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>6422.418</v>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>278.385</v>
+      </c>
+      <c r="D32" s="14">
+        <f>B32+C32*B31</f>
+        <v/>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>EGP tranche, dollar tranche, and the two in one currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Spent by 31 March 2026 (construction in progress)</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>5653.51</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="D34" s="14">
+        <f>D32-B33</f>
+        <v/>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>THE PROJECT PATH'S LAST YEAR is this less the four before it, so the path completes the programme by construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="39" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>The two shaded years at the top are the answer to the question this block exists to settle. With nothing being built, this plant cost EGP 80.8m and then EGP 42.5m a year to keep running. Everything above that is the new complex, and it stops when the complex is finished.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2297,19 +2565,19 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.85</v>
+        <v>-2.38</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-3.09</v>
+        <v>-2.61</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-3.31</v>
+        <v>-2.83</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-3.45</v>
+        <v>-2.97</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-3.59</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="7">
@@ -2319,19 +2587,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-1.31</v>
+        <v>-0.82</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-1.65</v>
+        <v>-1.16</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-1.97</v>
+        <v>-1.48</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-2.18</v>
+        <v>-1.68</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-2.38</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="8">
@@ -2341,19 +2609,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.22</v>
+        <v>0.74</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>-0.22</v>
+        <v>0.3</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>-0.64</v>
+        <v>-0.12</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-0.91</v>
+        <v>-0.39</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>-1.17</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="9">
@@ -2363,19 +2631,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.37</v>
+        <v>0.9</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="10">
@@ -2385,19 +2653,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2.65</v>
+        <v>3.21</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>2.04</v>
+        <v>2.59</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -2448,10 +2716,10 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.1358918966344949</v>
+        <v>0.1358901891583095</v>
       </c>
       <c r="D17" s="11">
-        <f>C17--0.7910702774432968</f>
+        <f>C17--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -2467,10 +2735,10 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>-1.481156639241684</v>
+        <v>-1.481160623940792</v>
       </c>
       <c r="D18" s="11">
-        <f>C18--0.7910702774432968</f>
+        <f>C18--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -2486,10 +2754,10 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>-0.8138333100334084</v>
+        <v>-0.8138361700374018</v>
       </c>
       <c r="D19" s="11">
-        <f>C19--0.7910702774432968</f>
+        <f>C19--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -2505,10 +2773,10 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>-0.1534648537287934</v>
+        <v>-0.1534666495592875</v>
       </c>
       <c r="D20" s="11">
-        <f>C20--0.7910702774432968</f>
+        <f>C20--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -2524,10 +2792,10 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>-2.579330601493619</v>
+        <v>-2.579333461497612</v>
       </c>
       <c r="D21" s="11">
-        <f>C21--0.7910702774432968</f>
+        <f>C21--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -2543,10 +2811,10 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>-0.6425820828037434</v>
+        <v>-0.6425849428077367</v>
       </c>
       <c r="D22" s="11">
-        <f>C22--0.7910702774432968</f>
+        <f>C22--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -2562,10 +2830,10 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>-1.566590242157883</v>
+        <v>-1.566593102161876</v>
       </c>
       <c r="D23" s="11">
-        <f>C23--0.7910702774432968</f>
+        <f>C23--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -2581,10 +2849,10 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>-0.2216206875244034</v>
+        <v>-0.2216235475283967</v>
       </c>
       <c r="D24" s="11">
-        <f>C24--0.7910702774432968</f>
+        <f>C24--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -2603,7 +2871,7 @@
         <v>-1.00506105644039</v>
       </c>
       <c r="D25" s="11">
-        <f>C25--0.7910702774432968</f>
+        <f>C25--0.7910731374472902</f>
         <v/>
       </c>
     </row>
@@ -3314,7 +3582,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.10075665145649</v>
+        <v>0.1007566615804626</v>
       </c>
     </row>
     <row r="26">
@@ -3659,7 +3927,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>-0.7910702774432968</v>
+        <v>-0.7910731374472902</v>
       </c>
     </row>
     <row r="24">
@@ -5675,8 +5943,9 @@
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C108" s="13" t="n">
-        <v>2598.8</v>
+      <c r="C108" s="14">
+        <f>'Cash Flow'!B30</f>
+        <v/>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
@@ -5755,8 +6024,9 @@
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C112" s="13" t="n">
-        <v>2489.4</v>
+      <c r="C112" s="14">
+        <f>'Cash Flow'!D34-(C108+C109+C110+C111)</f>
+        <v/>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
@@ -5775,8 +6045,9 @@
           <t>% of revenue</t>
         </is>
       </c>
-      <c r="C113" s="15" t="n">
-        <v>0.01115699027054101</v>
+      <c r="C113" s="8">
+        <f>'Cash Flow'!D28</f>
+        <v/>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
@@ -8113,7 +8384,7 @@
         <v/>
       </c>
       <c r="D36" s="14">
-        <f>SUM(B17:F17)+7259.369324</f>
+        <f>SUM(B17:F17)+7259.375005</f>
         <v/>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
@@ -32,9 +32,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
@@ -123,7 +123,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -132,23 +132,23 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1343,23 +1343,23 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>B5*'Assumptions'!C119/365</f>
+        <f>B5*'Assumptions'!C135/365</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>C5*'Assumptions'!C119/365</f>
+        <f>C5*'Assumptions'!C135/365</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>D5*'Assumptions'!C119/365</f>
+        <f>D5*'Assumptions'!C135/365</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>E5*'Assumptions'!C119/365</f>
+        <f>E5*'Assumptions'!C135/365</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>F5*'Assumptions'!C119/365</f>
+        <f>F5*'Assumptions'!C135/365</f>
         <v/>
       </c>
     </row>
@@ -1370,23 +1370,23 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>B6*'Assumptions'!C120/365</f>
+        <f>B6*'Assumptions'!C136/365</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>C6*'Assumptions'!C120/365</f>
+        <f>C6*'Assumptions'!C136/365</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>D6*'Assumptions'!C120/365</f>
+        <f>D6*'Assumptions'!C136/365</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>E6*'Assumptions'!C120/365</f>
+        <f>E6*'Assumptions'!C136/365</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>F6*'Assumptions'!C120/365</f>
+        <f>F6*'Assumptions'!C136/365</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>B6*'Assumptions'!C121/365</f>
+        <f>B6*'Assumptions'!C137/365</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>C6*'Assumptions'!C121/365</f>
+        <f>C6*'Assumptions'!C137/365</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>D6*'Assumptions'!C121/365</f>
+        <f>D6*'Assumptions'!C137/365</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>E6*'Assumptions'!C121/365</f>
+        <f>E6*'Assumptions'!C137/365</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>F6*'Assumptions'!C121/365</f>
+        <f>F6*'Assumptions'!C137/365</f>
         <v/>
       </c>
     </row>
@@ -1447,11 +1447,11 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Opening net working capital, FY2025/26E</t>
+          <t>Opening net working capital, 31 March 2026 as reported</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>2071.224822596537</v>
+        <v>3069.424</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
           <t>FY2021/22</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="20" t="n">
         <v>80.847245</v>
       </c>
       <c r="C22" s="13" t="n">
@@ -1570,7 +1570,7 @@
           <t>FY2022/23</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="20" t="n">
         <v>42.470154</v>
       </c>
       <c r="C23" s="13" t="n">
@@ -1592,7 +1592,7 @@
           <t>FY2023/24</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="20" t="n">
         <v>2396.608259</v>
       </c>
       <c r="C24" s="13" t="n">
@@ -1614,7 +1614,7 @@
           <t>FY2024/25</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="20" t="n">
         <v>1545.053761</v>
       </c>
       <c r="C25" s="13" t="n">
@@ -1636,7 +1636,7 @@
           <t>9M FY2025/26</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="20" t="n">
         <v>1949.134461</v>
       </c>
       <c r="C26" s="13" t="n">
@@ -1730,7 +1730,7 @@
       <c r="B32" s="13" t="n">
         <v>6422.418</v>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="20" t="n">
         <v>278.385</v>
       </c>
       <c r="D32" s="14">
@@ -2114,23 +2114,23 @@
         </is>
       </c>
       <c r="B15" s="29">
-        <f>'Assumptions'!C26</f>
+        <f>'Assumptions'!C33</f>
         <v/>
       </c>
       <c r="C15" s="29">
-        <f>'Assumptions'!C27</f>
+        <f>'Assumptions'!C34</f>
         <v/>
       </c>
       <c r="D15" s="29">
-        <f>'Assumptions'!C28</f>
+        <f>'Assumptions'!C35</f>
         <v/>
       </c>
       <c r="E15" s="29">
-        <f>'Assumptions'!C29</f>
+        <f>'Assumptions'!C36</f>
         <v/>
       </c>
       <c r="F15" s="29">
-        <f>'Assumptions'!C30</f>
+        <f>'Assumptions'!C37</f>
         <v/>
       </c>
     </row>
@@ -2565,19 +2565,19 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.38</v>
+        <v>-2.64</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-2.61</v>
+        <v>-2.74</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-2.83</v>
+        <v>-2.85</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-2.97</v>
+        <v>-2.91</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-3.12</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="7">
@@ -2587,19 +2587,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-0.82</v>
+        <v>-1.06</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-1.16</v>
+        <v>-1.25</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-1.48</v>
+        <v>-1.44</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-1.68</v>
+        <v>-1.56</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-1.88</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="8">
@@ -2609,19 +2609,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.74</v>
+        <v>0.52</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-0.39</v>
+        <v>-0.21</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>-0.65</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="9">
@@ -2631,19 +2631,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="E9" s="12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0.58</v>
       </c>
     </row>
     <row r="10">
@@ -2653,19 +2653,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>3.86</v>
+        <v>3.67</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -2681,6 +2681,15 @@
           <t>THE CONTESTED CONSTRUCTIONS — one component moved, model re-run</t>
         </is>
       </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>The published answer</t>
+        </is>
+      </c>
+      <c r="D15" s="11">
+        <f>'DCF'!B44</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2716,10 +2725,10 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.1358901891583095</v>
+        <v>-0.01815018750557796</v>
       </c>
       <c r="D17" s="11">
-        <f>C17--0.7910731374472902</f>
+        <f>C17-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2735,10 +2744,10 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>-1.481160623940792</v>
+        <v>-1.167721151771788</v>
       </c>
       <c r="D18" s="11">
-        <f>C18--0.7910731374472902</f>
+        <f>C18-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2754,10 +2763,10 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>-0.8138361700374018</v>
+        <v>-0.6670929341943478</v>
       </c>
       <c r="D19" s="11">
-        <f>C19--0.7910731374472902</f>
+        <f>C19-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2773,10 +2782,10 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>-0.1534666495592875</v>
+        <v>-0.1993221562101967</v>
       </c>
       <c r="D20" s="11">
-        <f>C20--0.7910731374472902</f>
+        <f>C20-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2792,10 +2801,10 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>-2.579333461497612</v>
+        <v>-2.553287069645033</v>
       </c>
       <c r="D21" s="11">
-        <f>C21--0.7910731374472902</f>
+        <f>C21-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2811,10 +2820,10 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>-0.6425849428077367</v>
+        <v>-0.4499628389347562</v>
       </c>
       <c r="D22" s="11">
-        <f>C22--0.7910731374472902</f>
+        <f>C22-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2830,10 +2839,10 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>-1.566593102161876</v>
+        <v>-1.48122464015131</v>
       </c>
       <c r="D23" s="11">
-        <f>C23--0.7910731374472902</f>
+        <f>C23-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2849,10 +2858,10 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>-0.2216235475283967</v>
+        <v>-0.4056928790197533</v>
       </c>
       <c r="D24" s="11">
-        <f>C24--0.7910731374472902</f>
+        <f>C24-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2868,10 +2877,10 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>-1.00506105644039</v>
+        <v>-0.8996788650758137</v>
       </c>
       <c r="D25" s="11">
-        <f>C25--0.7910731374472902</f>
+        <f>C25-$D$15</f>
         <v/>
       </c>
     </row>
@@ -2955,7 +2964,7 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>'Summary'!B16/16206.086</f>
+        <f>'Summary'!B16/'Fundamental Valuation'!B5</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr"/>
@@ -2983,7 +2992,7 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>'Assumptions'!C84</f>
+        <f>'Assumptions'!C91</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -3055,7 +3064,7 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>'DCF'!B14*1000000/1986578999</f>
+        <f>'DCF'!B14*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C13" s="9" t="inlineStr"/>
@@ -3067,7 +3076,7 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>'DCF'!F14*1000000/1986578999</f>
+        <f>'DCF'!F14*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr"/>
@@ -3277,7 +3286,7 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>'Assumptions'!C62</f>
+        <f>'Assumptions'!C69</f>
         <v/>
       </c>
     </row>
@@ -3582,7 +3591,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.1007566615804626</v>
+        <v>0.07933489569564534</v>
       </c>
     </row>
     <row r="26">
@@ -3602,7 +3611,7 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>'Assumptions'!C95</f>
+        <f>'Assumptions'!C102</f>
         <v/>
       </c>
     </row>
@@ -3613,7 +3622,7 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>'Assumptions'!C93*'Assumptions'!C85+'Assumptions'!C94*'Assumptions'!C91*(1-'Assumptions'!C92)</f>
+        <f>'Assumptions'!C100*'Assumptions'!C92+'Assumptions'!C101*'Assumptions'!C98*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
     </row>
@@ -3703,7 +3712,7 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>B5*1000000/1986578999</f>
+        <f>B5*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr"/>
@@ -3815,7 +3824,7 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>'Assumptions'!C84</f>
+        <f>'Assumptions'!C91</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -3831,7 +3840,7 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>'Assumptions'!C102</f>
+        <f>'Assumptions'!C109</f>
         <v/>
       </c>
       <c r="C15" s="9" t="inlineStr"/>
@@ -3887,7 +3896,7 @@
         </is>
       </c>
       <c r="B19" s="11">
-        <f>B14*0+13.98*1986578999/1000000/B5</f>
+        <f>B14*0+'Assumptions'!C7*'Assumptions'!C6/1000000/B5</f>
         <v/>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -3927,7 +3936,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>-0.7910731374472902</v>
+        <v>-0.6670929341943478</v>
       </c>
     </row>
     <row r="24">
@@ -3937,7 +3946,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>2.491915450464006</v>
+        <v>3.337010452983641</v>
       </c>
     </row>
     <row r="25">
@@ -3947,7 +3956,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>0</v>
+        <v>0.5772439672035078</v>
       </c>
     </row>
     <row r="26">
@@ -3957,7 +3966,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>6.918193137103221</v>
+        <v>7.340407384570012</v>
       </c>
     </row>
     <row r="27">
@@ -4003,7 +4012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4051,1168 +4060,1155 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>CAPACITY AND VOLUME</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="14" customHeight="1">
+          <t>THE CAPITALISATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Urea design capacity</t>
+          <t>Shares outstanding</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>tonnes/year</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>574875</v>
+        <v>1986578999</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Constructed: 1,575 t/day contractual plate times 365 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 14 share capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Ammonia design capacity</t>
+          <t>Anchor price</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>tonnes/year</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>438000</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>13.98</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 28</t>
+          <t>Exchange close, from the study's own price library</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ammonia per tonne of urea</t>
+          <t>Exchange rate, FY2024/25 average</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>tonnes</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>0.619889556570605</v>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>49</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Constructed: FY2024/25 ammonia output divided by FY2024/25 urea output, both from the auditor's product cost table</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>Constructed: the rate that reconciles note 20 export revenue to the disclosed export price and the implied export tonnage</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Urea capacity utilisation — FY2026/27</t>
+          <t>Normalised-earnings multiple, low</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>% of plate</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>0.913</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>Multiple applied to mid-cycle profit after tax, low end</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Urea capacity utilisation — FY2027/28</t>
+          <t>Normalised-earnings multiple, central</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>% of plate</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>0.922</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>Multiple applied to mid-cycle profit after tax, central</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Urea capacity utilisation — FY2028/29</t>
+          <t>Normalised-earnings multiple, high</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>% of plate</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>0.93</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Urea capacity utilisation — FY2029/30</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>% of plate</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+          <t>Multiple applied to mid-cycle profit after tax, high end</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>CAPACITY AND VOLUME</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Urea capacity utilisation — FY2030/31</t>
+          <t>Urea design capacity</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>% of plate</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>0.948</v>
+          <t>tonnes/year</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>574875</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
+          <t>Constructed: 1,575 t/day contractual plate times 365 days</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Subsidised deliveries — FY2026/27</t>
+          <t>Ammonia design capacity</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>tonnes</t>
+          <t>tonnes/year</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>155000</v>
+        <v>438000</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 28</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t>Ammonia per tonne of urea</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>0.619889556570605</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: FY2024/25 ammonia output divided by FY2024/25 urea output, both from the auditor's product cost table</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Urea capacity utilisation — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>% of plate</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Urea capacity utilisation — FY2027/28</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>% of plate</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Urea capacity utilisation — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>% of plate</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Urea capacity utilisation — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>% of plate</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Urea capacity utilisation — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>% of plate</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: utilisation path. Audited output ran 586.4kt in FY2022/23 (2% above plate), 521.9kt in FY2023/24 and 513.4kt in FY2024/25; the path never returns to plate because the summer gas curtailment is structural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Subsidised deliveries — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>155000</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
           <t>Subsidised deliveries — FY2027/28</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C22" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Subsidised deliveries — FY2028/29</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C23" s="13" t="n">
         <v>165000</v>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Subsidised deliveries — FY2029/30</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C24" s="13" t="n">
         <v>170000</v>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Subsidised deliveries — FY2030/31</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C25" s="13" t="n">
         <v>175000</v>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: subsidised delivery path. The company met 147kt of a 322kt requirement in the fourteen months to August 2025, a 46% compliance rate the forecast does not assume away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Local free-market volume — FY2026/27</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C26" s="13" t="n">
         <v>40000</v>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Local free-market volume path from the 37.1kt implied for FY2024/25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: local free-market volume path from the 37.1kt implied for FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Local free-market volume — FY2027/28</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C27" s="13" t="n">
         <v>41000</v>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Local free-market volume path from the 37.1kt implied for FY2024/25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: local free-market volume path from the 37.1kt implied for FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Local free-market volume — FY2028/29</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C28" s="13" t="n">
         <v>42000</v>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Local free-market volume path from the 37.1kt implied for FY2024/25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: local free-market volume path from the 37.1kt implied for FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Local free-market volume — FY2029/30</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C29" s="13" t="n">
         <v>43000</v>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Local free-market volume path from the 37.1kt implied for FY2024/25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: local free-market volume path from the 37.1kt implied for FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Local free-market volume — FY2030/31</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C30" s="13" t="n">
         <v>44000</v>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Local free-market volume path from the 37.1kt implied for FY2024/25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: local free-market volume path from the 37.1kt implied for FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>PRICES</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Export urea price — FY2026/27</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>US$/tonne</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="n">
-        <v>530</v>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Export urea price — FY2027/28</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>US$/tonne</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="n">
-        <v>500</v>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Export urea price — FY2028/29</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>US$/tonne</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="n">
-        <v>470</v>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Export urea price — FY2029/30</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>US$/tonne</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>450</v>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Export urea price — FY2030/31</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>US$/tonne</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="n">
-        <v>440</v>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian pounds per US dollar — FY2026/27</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>EGP/US$</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Currency path at 4.5% depreciation a year from the spot rate — the same wedge used to carry the dollar debt at local-equivalent cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian pounds per US dollar — FY2027/28</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>EGP/US$</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Currency path at 4.5% depreciation a year from the spot rate — the same wedge used to carry the dollar debt at local-equivalent cost.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Egyptian pounds per US dollar — FY2028/29</t>
+          <t>Export urea price — FY2026/27</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>EGP/US$</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>56.7</v>
+          <t>US$/tonne</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="n">
+        <v>530</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Currency path at 4.5% depreciation a year from the spot rate — the same wedge used to carry the dollar debt at local-equivalent cost.</t>
+          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Egyptian pounds per US dollar — FY2029/30</t>
+          <t>Export urea price — FY2027/28</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>EGP/US$</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>59.2</v>
+          <t>US$/tonne</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>500</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Currency path at 4.5% depreciation a year from the spot rate — the same wedge used to carry the dollar debt at local-equivalent cost.</t>
+          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Egyptian pounds per US dollar — FY2030/31</t>
+          <t>Export urea price — FY2028/29</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
+          <t>US$/tonne</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>470</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Export urea price — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>US$/tonne</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>450</v>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Export urea price — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>US$/tonne</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>440</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Egyptian pounds per US dollar — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>EGP/US$</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>Currency path at 4.5% depreciation a year from the spot rate — the same wedge used to carry the dollar debt at local-equivalent cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Export duty</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>% of export value</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>2026 replacement of the shortfall levy with an ad-valorem duty tied to the global price</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Subsidised price — FY2026/27</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>EGP/tonne</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>7526</v>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Subsidised price — FY2027/28</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>EGP/tonne</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="n">
-        <v>8429</v>
+      <c r="C38" s="12" t="n">
+        <v>53.4853515625</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="14" customHeight="1">
+          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Subsidised price — FY2028/29</t>
+          <t>Egyptian pounds per US dollar — FY2027/28</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>EGP/tonne</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>9272</v>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>56.67149066925049</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="14" customHeight="1">
+          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Subsidised price — FY2029/30</t>
+          <t>Egyptian pounds per US dollar — FY2028/29</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>EGP/tonne</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="n">
-        <v>10106</v>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>59.49399655219167</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="14" customHeight="1">
+          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Subsidised price — FY2030/31</t>
+          <t>Egyptian pounds per US dollar — FY2029/30</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>EGP/tonne</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="n">
-        <v>10915</v>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>62.16657842855966</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
+          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Local free price as % of export parity</t>
+          <t>Egyptian pounds per US dollar — FY2030/31</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>0.9</v>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>64.95921769390512</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Local free-market urea clears at about 90% of export parity, implied by the FY2024/25 note-20 local revenue net of the subsidised and nitrate legs</t>
+          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Nitrate volume — FY2026/27</t>
+          <t>Export duty</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>tonnes</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n">
-        <v>26000</v>
+          <t>% of export value</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+          <t>2026 replacement of the shortfall levy with an ad-valorem duty tied to the global price</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Nitrate volume — FY2027/28</t>
+          <t>Subsidised price — FY2026/27</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>tonnes</t>
+          <t>EGP/tonne</t>
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26000</v>
+        <v>7526</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Nitrate volume — FY2028/29</t>
+          <t>Subsidised price — FY2027/28</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>tonnes</t>
+          <t>EGP/tonne</t>
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>26000</v>
+        <v>8429</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Nitrate volume — FY2029/30</t>
+          <t>Subsidised price — FY2028/29</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>tonnes</t>
+          <t>EGP/tonne</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>26000</v>
+        <v>9272</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>Subsidised price — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>EGP/tonne</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>10106</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Subsidised price — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>EGP/tonne</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>10915</v>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Local free price as % of export parity</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: local free-market urea clears at about 90% of export parity, implied by the FY2024/25 note-20 local revenue net of the subsidised and nitrate legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Nitrate volume — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Nitrate volume — FY2027/28</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Nitrate volume — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Nitrate volume — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
           <t>Nitrate volume — FY2030/31</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C47" s="13" t="n">
+      <c r="C54" s="13" t="n">
         <v>26000</v>
       </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>Nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Nitrate price, FY2024/25 basis</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>EGP/tonne</t>
         </is>
       </c>
-      <c r="C48" s="13" t="n">
+      <c r="C55" s="13" t="n">
         <v>20000</v>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>Implied by the note-20 local revenue net of the subsidised and free-market urea legs; indexed forward on the currency</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Other revenue — FY2026/27</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C56" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Other revenue — FY2027/28</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n">
+      <c r="C57" s="20" t="n">
         <v>152</v>
       </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>Merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Other revenue — FY2028/29</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="n">
-        <v>163</v>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>Merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Other revenue — FY2029/30</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>174</v>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>Merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="14" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Other revenue — FY2030/31</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C53" s="21" t="n">
-        <v>186</v>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>Merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>COST STACK — ONE ESCALATOR PER PHYSICAL DRIVER</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="48" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Gas per tonne of ammonia</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="n">
-        <v>1292</v>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>Constructed and FLAGGED: the statements give a single materials line and do not split gas from the rest. Gas is set at three quarters of that line, which implies 1,292 m3 per tonne of ammonia — inside the auditor's own disclosed 1,025 to 1,771 range. This is the largest modelled allocation in the study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Realised gas price</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>US$/mmBtu</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="n">
-        <v>4.68</v>
-      </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Constructed: the company's own Q1 disclosure values 31,313,235 m3 of lost gas at EGP 251m, or EGP 8.016/m3, which converts to about US$4.68/mmBtu at the prevailing rate — below the US$5.75 contract price, which the study carries as its downside case</t>
+          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
+          <t>Other revenue — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="n">
+        <v>163</v>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Other revenue — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="n">
+        <v>174</v>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Other revenue — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="n">
+        <v>186</v>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>COST STACK — ONE ESCALATOR PER PHYSICAL DRIVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Gas per tonne of ammonia</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="n">
+        <v>1292</v>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Constructed and FLAGGED: the statements give a single materials line and do not split gas from the rest. Gas is set at three quarters of that line, which implies 1,292 m3 per tonne of ammonia — inside the auditor's own disclosed 1,025 to 1,771 range. This is the largest modelled allocation in the study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Realised gas price</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>US$/mmBtu</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: the company's own Q1 disclosure values 31,313,235 m3 of lost gas at EGP 251m, or EGP 8.016/m3, which converts to about US$4.68/mmBtu at the prevailing rate — below the US$5.75 contract price, which the study carries as its downside case</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
           <t>Energy conversion</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>mmBtu per m3</t>
         </is>
       </c>
-      <c r="C58" s="22" t="n">
+      <c r="C65" s="22" t="n">
         <v>0.03531</v>
       </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>Standard gross calorific conversion</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Other materials per tonne of urea</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="n">
-        <v>2141.977268521675</v>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>The FY2024/25 materials line less modelled gas, over urea output: packaging, catalysts and consumable spares</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Wages in cost of sales, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n">
-        <v>212.857</v>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 21</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Purchased services, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C61" s="21" t="n">
-        <v>62.557</v>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 21</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Inland freight per export tonne</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>1741.725316670984</v>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 22 freight and commissions over the implied export tonnage</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Other selling cost, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C63" s="21" t="n">
-        <v>176.305</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 22 selling materials, wages and other selling expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Administrative expense, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C64" s="21" t="n">
-        <v>359.624</v>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), income statement</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Stoppage and abnormal gas cost — FY2026/27</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C65" s="21" t="n">
-        <v>150</v>
-      </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+          <t>Constructed: standard gross calorific conversion</t>
         </is>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal gas cost — FY2027/28</t>
+          <t>Other materials per tonne of urea</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C66" s="21" t="n">
-        <v>120</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>2141.977268521675</v>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+          <t>The FY2024/25 materials line less modelled gas, over urea output: packaging, catalysts and consumable spares</t>
         </is>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal gas cost — FY2028/29</t>
+          <t>Wages in cost of sales, FY2024/25</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -5220,19 +5216,19 @@
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C67" s="21" t="n">
-        <v>100</v>
+      <c r="C67" s="20" t="n">
+        <v>212.857</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 21</t>
         </is>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal gas cost — FY2029/30</t>
+          <t>Purchased services, FY2024/25</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -5240,146 +5236,179 @@
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C68" s="21" t="n">
-        <v>90</v>
+      <c r="C68" s="20" t="n">
+        <v>62.557</v>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 21</t>
         </is>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
+          <t>Inland freight per export tonne</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="n">
+        <v>1741.725316670984</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 22 freight and commissions over the implied export tonnage</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Other selling cost, FY2024/25</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="n">
+        <v>176.305</v>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 22 selling materials, wages and other selling expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Administrative expense, FY2024/25</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="n">
+        <v>359.624</v>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), income statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Stoppage and abnormal gas cost — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Stoppage and abnormal gas cost — FY2027/28</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="n">
+        <v>120</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Stoppage and abnormal gas cost — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Stoppage and abnormal gas cost — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
           <t>Stoppage and abnormal gas cost — FY2030/31</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C69" s="21" t="n">
+      <c r="C76" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>Stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="14" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian inflation — FY2026/27</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian inflation — FY2027/28</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian inflation — FY2028/29</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="14" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian inflation — FY2029/30</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian inflation — FY2030/31</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>COST OF CAPITAL</t>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Observed ten-year government yield</t>
+          <t>Egyptian inflation — FY2026/27</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -5387,19 +5416,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C77" s="23" t="n">
-        <v>0.23</v>
+      <c r="C77" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Egypt ten-year government bond yield, market quote</t>
+          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Sovereign default spread, rating basis</t>
+          <t>Egyptian inflation — FY2027/28</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -5407,19 +5436,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C78" s="23" t="n">
-        <v>0.06372478453347744</v>
+      <c r="C78" s="15" t="n">
+        <v>0.08500000000000001</v>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Country risk premium workbook, original file, Egypt row, adjusted default spread</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
+          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="14" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Normalised risk-free rate, rating basis</t>
+          <t>Egyptian inflation — FY2028/29</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -5427,20 +5456,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C79" s="16">
-        <f>'Assumptions'!C77-'Assumptions'!C78</f>
-        <v/>
+      <c r="C79" s="15" t="n">
+        <v>0.075</v>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Country risk enters ONCE, through the premium below. Using the raw local yield with a country-loaded premium would charge Egypt's sovereign risk twice.</t>
+          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium, rating basis</t>
+          <t>Egyptian inflation — FY2029/30</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -5448,19 +5476,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C80" s="23" t="n">
-        <v>0.139376943200201</v>
+      <c r="C80" s="15" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Country risk premium workbook, original file, Egypt row, rating basis total equity risk premium</t>
+          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Sovereign default spread, CDS basis</t>
+          <t>Egyptian inflation — FY2030/31</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -5468,111 +5496,87 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C81" s="23" t="n">
-        <v>0.0355</v>
+      <c r="C81" s="15" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Country risk premium workbook, original file, Egypt row, ten-year CDS spread</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="14" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Equity risk premium, CDS basis</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+          <t>Domestic inflation converging from the June 2026 print on the central bank's target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>COST OF CAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Observed ten-year government yield</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C82" s="23" t="n">
-        <v>0.09424719428808419</v>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>Country risk premium workbook, original file, Egypt row, CDS basis total equity risk premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C83" s="20" t="n">
-        <v>1.052664590352939</v>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>Own-stock weekly regression, 257 observations over five years against an equal-weight index of 35 Egyptian names with the subject excluded, R-squared 0.283, standard error 0.105</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>Cost of equity, rating basis</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="C84" s="23" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Egypt ten-year government bond yield, market quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Sovereign default spread, rating basis</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C84" s="16">
-        <f>'Assumptions'!C79+'Assumptions'!C83*'Assumptions'!C80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>Cost of equity, CDS basis</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="C85" s="23" t="n">
+        <v>0.06372478453347744</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Country risk premium workbook, original file, Egypt row, adjusted default spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Normalised risk-free rate, rating basis</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C85" s="16">
-        <f>'Assumptions'!C77-'Assumptions'!C81+'Assumptions'!C83*'Assumptions'!C82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt, local currency</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C86" s="23" t="n">
-        <v>0.194</v>
+      <c r="C86" s="16">
+        <f>'Assumptions'!C84-'Assumptions'!C85</f>
+        <v/>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Constructed: EGP 96,896,001 of interest on the EGP 500,000,000 holding-company facility drawn in FY2024/25 — the company's own latest local borrowing</t>
+          <t>Country risk enters ONCE, through the premium below. Using the raw local yield with a country-loaded premium would charge Egypt's sovereign risk twice.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt, dollar tranche, in dollars</t>
+          <t>Equity risk premium, rating basis</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -5581,18 +5585,18 @@
         </is>
       </c>
       <c r="C87" s="23" t="n">
-        <v>0.117</v>
+        <v>0.139376943200201</v>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Constructed: EGP 1,338.0m of FY2024/25 interest on a mean dollar balance of about US$233m</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="24" customHeight="1">
+          <t>Country risk premium workbook, original file, Egypt row, rating basis total equity risk premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="14" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Expected currency depreciation</t>
+          <t>Sovereign default spread, CDS basis</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -5601,18 +5605,18 @@
         </is>
       </c>
       <c r="C88" s="23" t="n">
-        <v>0.045</v>
+        <v>0.0341</v>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Constructed: the central bank's 7% inflation target against about 2.4% in the United States. The SAME wedge drives the currency path in the revenue build, so the two cannot diverge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
+          <t>Country risk premium workbook, original file, Egypt row, ten-year CDS spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Dollar debt at local-equivalent cost</t>
+          <t>Equity risk premium, CDS basis</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -5620,35 +5624,39 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C89" s="16">
-        <f>(1+'Assumptions'!C87)*(1+'Assumptions'!C88)-1</f>
-        <v/>
+      <c r="C89" s="23" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Country risk premium workbook, original file, Egypt row, equity risk premium based on the sovereign credit default swap. CORRECTED 9 August 2026: the study had 9.4247%, reconstructed from a 3.55% spread the file does not carry. Damodaran's Egypt row reads 3.41% and 9.41%.</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Share of debt in local currency</t>
+          <t>Beta</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="n">
-        <v>0.003135811265216677</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C90" s="21" t="n">
+        <v>1.052664590352939</v>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>The pound tranche of the project loan was repaid in June 2024, so the book is almost entirely dollar</t>
+          <t>Own-stock weekly regression, 257 observations over five years against an equal-weight index of 35 Egyptian names with the subject excluded, R-squared 0.283, standard error 0.105</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Blended pre-tax cost of debt</t>
+          <t>Cost of equity, rating basis</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -5657,14 +5665,14 @@
         </is>
       </c>
       <c r="C91" s="16">
-        <f>'Assumptions'!C90*'Assumptions'!C86+(1-'Assumptions'!C90)*'Assumptions'!C89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="24" customHeight="1">
+        <f>'Assumptions'!C86+'Assumptions'!C90*'Assumptions'!C87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Tax rate</t>
+          <t>Cost of equity, CDS basis</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -5672,19 +5680,15 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C92" s="15" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-16 income tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="14" customHeight="1">
+      <c r="C92" s="16">
+        <f>'Assumptions'!C84-'Assumptions'!C88+'Assumptions'!C90*'Assumptions'!C89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="24" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Equity weight</t>
+          <t>Cost of debt, local currency</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -5692,19 +5696,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C93" s="15" t="n">
-        <v>0.6548338567778519</v>
+      <c r="C93" s="23" t="n">
+        <v>0.194</v>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Market-value equity over market-value equity plus debt</t>
+          <t>Constructed: EGP 96,896,001 of interest on the EGP 500,000,000 holding-company facility drawn in FY2024/25 — the company's own latest local borrowing</t>
         </is>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Debt weight</t>
+          <t>Cost of debt, dollar tranche, in dollars</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -5712,19 +5716,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C94" s="15" t="n">
-        <v>0.3451661432221481</v>
+      <c r="C94" s="23" t="n">
+        <v>0.117</v>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>One less the equity weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
+          <t>Constructed: EGP 1,338.0m of FY2024/25 interest on a mean dollar balance of about US$233m</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital, year one</t>
+          <t>Expected currency depreciation</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -5732,15 +5736,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C95" s="16">
-        <f>'Assumptions'!C93*'Assumptions'!C84+'Assumptions'!C94*'Assumptions'!C91*(1-'Assumptions'!C92)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="14" customHeight="1">
+      <c r="C95" s="23" t="n">
+        <v>0.025390625</v>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: the central bank's LONG-RUN 5% target against about 2.4% in the United States, on the same relative-purchasing-power identity the study states. CORRECTED 9 August 2026: the study previously asserted 4.5% flat while stating a derivation that produces a different number in every year. The wedge is now computed from the identity rather than asserted, and the currency path is built from it year by year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Long-run inflation</t>
+          <t>Dollar debt at local-equivalent cost</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -5748,19 +5756,15 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C96" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>Central bank published medium-term inflation target</t>
-        </is>
+      <c r="C96" s="16">
+        <f>(1+'Assumptions'!C94)*(1+'Assumptions'!C95)-1</f>
+        <v/>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Long-run real rate</t>
+          <t>Share of debt in local currency</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -5769,448 +5773,761 @@
         </is>
       </c>
       <c r="C97" s="15" t="n">
-        <v>0.035</v>
+        <v>0.003135811265216677</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Long-run emerging-market real policy rate, used to build the terminal risk-free rate from its own components rather than from a spot yield</t>
+          <t>The pound tranche of the project loan was repaid in June 2024, so the book is almost entirely dollar</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
+          <t>Blended pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C98" s="16">
+        <f>'Assumptions'!C97*'Assumptions'!C93+(1-'Assumptions'!C97)*'Assumptions'!C96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="24" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-16 income tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Equity weight</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="n">
+        <v>0.6548338567778519</v>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Market-value equity over market-value equity plus debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>Debt weight</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="n">
+        <v>0.3451661432221481</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>One less the equity weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Cost of capital, year one</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C102" s="16">
+        <f>'Assumptions'!C100*'Assumptions'!C91+'Assumptions'!C101*'Assumptions'!C98*(1-'Assumptions'!C99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Long-run inflation</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Central bank published medium-term inflation target</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Long-run real rate</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: long-run emerging-market real policy rate, used to build the terminal risk-free rate from its own components rather than from a spot yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
           <t>Terminal normalised risk-free rate</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C98" s="16">
-        <f>(1+'Assumptions'!C96)*(1+'Assumptions'!C97)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
+      <c r="C105" s="16">
+        <f>(1+'Assumptions'!C103)*(1+'Assumptions'!C104)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>Long-run dollar cost of debt</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C99" s="23" t="n">
+      <c r="C106" s="23" t="n">
         <v>0.09</v>
       </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>Long-run corporate dollar cost of debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: long-run corporate dollar cost of debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>Terminal cost of debt, local-equivalent</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C100" s="16">
-        <f>(1+'Assumptions'!C99)*(1+'Assumptions'!C88)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="C107" s="16">
+        <f>(1+'Assumptions'!C106)*(1+'Assumptions'!C95)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>TERMINAL COST OF CAPITAL</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C101" s="16">
-        <f>'Assumptions'!C93*('Assumptions'!C98+'Assumptions'!C83*'Assumptions'!C80)+'Assumptions'!C94*'Assumptions'!C100*(1-'Assumptions'!C92)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
+      <c r="C108" s="16">
+        <f>'Assumptions'!C100*('Assumptions'!C105+'Assumptions'!C90*'Assumptions'!C87)+'Assumptions'!C101*'Assumptions'!C107*(1-'Assumptions'!C99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C102" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>Terminal growth set at the central bank's medium-term inflation target: nominal maintenance growth, no real growth assumed</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="24" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="C109" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Terminal growth set at the central bank's LONGEST-HORIZON published inflation target: 5% (+/-2) for Q4 2028. CORRECTED 9 August 2026 after external critique: the study previously used the 7% Q4-2026 target, which expires one quarter after the anchor date, as a perpetuity anchor -- and then defended it by calling 5% 'below the target', inverting the central bank's own target structure. A perpetuity takes the longest-horizon target there is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C103" s="15" t="n">
+      <c r="C110" s="15" t="n">
         <v>0.18</v>
       </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>Terminal return on invested capital, which sets the terminal reinvestment rate as growth divided by return on capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: terminal return on invested capital, which sets the terminal reinvestment rate as growth divided by return on capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>CAPITAL, WORKING CAPITAL AND THE PROJECT</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="113" ht="24" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>Depreciation charge, FY2024/25</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C106" s="21" t="n">
+      <c r="C113" s="20" t="n">
         <v>771.213</v>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 6 fixed-asset register</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>Amortisation, FY2024/25</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C107" s="21" t="n">
+      <c r="C114" s="20" t="n">
         <v>119.378</v>
       </c>
-      <c r="D107" s="9" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 10 usufruct intangible</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="48" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2026/27</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C108" s="14">
+      <c r="C115" s="14">
         <f>'Cash Flow'!B30</f>
         <v/>
       </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="48" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2027/28</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C109" s="13" t="n">
+      <c r="C116" s="13" t="n">
         <v>3100</v>
       </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="48" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2028/29</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C110" s="13" t="n">
+      <c r="C117" s="13" t="n">
         <v>3300</v>
       </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="48" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2029/30</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C111" s="13" t="n">
+      <c r="C118" s="13" t="n">
         <v>3200</v>
       </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="48" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2030/31</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C112" s="14">
-        <f>'Cash Flow'!D34-(C108+C109+C110+C111)</f>
-        <v/>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>Project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="72" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="C119" s="14">
+        <f>'Cash Flow'!D34-(C115+C116+C117+C118)</f>
+        <v/>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="24" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation escalation on the existing base</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: escalation on the existing depreciation base, reflecting ordinary additions to the plant already in service</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="24" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation rate on the new complex</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="C121" s="23" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-2 depreciation rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="48" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>New complex nameplate</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>tonnes/day</t>
+        </is>
+      </c>
+      <c r="C122" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>Operating days a year</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="n">
+        <v>330</v>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: operating days a year for a continuous nitrate line, net of the turnaround the company takes annually</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="24" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>Steady-state depreciation wedge in the terminal year</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: steady-state gap between the terminal inflation target and the currency wedge, held constant in the terminal year</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="24" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>The complex is completed and in service (1 = yes)</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
+      <c r="C125" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>Case switch. Zero in the capital-discipline column, where the plant is never finished and therefore never depreciated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Approved cost of the new complex</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="n">
+        <v>20341.668</v>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 18-3 — bank-approved investment cost, agreement of 25 June 2025; dual-currency tranches at the approval rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="72" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>% of revenue</t>
         </is>
       </c>
-      <c r="C113" s="8">
+      <c r="C127" s="8">
         <f>'Cash Flow'!D28</f>
         <v/>
       </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure as a share of revenue, RE-ANCHORED 9 August 2026 on the company's OWN pre-project cash-flow statements: EGP 123.3m spent across FY2021/22 and FY2022/23 on EGP 11,052.9m of revenue. The first issue of this study used a 3.0% mature-plant standard instead, which is 2.7 times what this company has ever spent to keep its plant running, and which no disclosure supports. The replacement-rate framing (gross fixed assets at the disclosed 3.95% machinery rate, 6.11% of revenue) is carried as the published alternative and as the downside case.</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
+    <row r="128" ht="36" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Wind-down cost if the programme is stopped</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C128" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: capital-discipline case only: the cost of stopping the programme in the first forecast year — contract settlement and site preservation. No filing states it; it is the study's estimate and is flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="24" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>Ammonia per tonne of nitrate</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C114" s="12" t="n">
+      <c r="C129" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>Ammonia per tonne of ammonium nitrate through the nitric-acid route plus direct neutralisation</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: ammonia per tonne of ammonium nitrate through the nitric-acid route plus direct neutralisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>Project nameplate (derived, not disclosed)</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>tonnes/year</t>
         </is>
       </c>
-      <c r="C115" s="14">
-        <f>('Assumptions'!C7-'Assumptions'!C6*'Assumptions'!C8)/'Assumptions'!C114</f>
-        <v/>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>Constructed and FLAGGED: no filing states the new plant's capacity. It is the ammonia design plate less the draw of urea at ITS design plate, converted at the ratio above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="14" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
+      <c r="C130" s="14">
+        <f>'Assumptions'!C122*'Assumptions'!C123</f>
+        <v/>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>Cross-check: nameplate derived from the ammonia surplus</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>tonnes/year</t>
+        </is>
+      </c>
+      <c r="C131" s="14">
+        <f>('Assumptions'!C14-'Assumptions'!C13*'Assumptions'!C15)/'Assumptions'!C129</f>
+        <v/>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>The construction the study used before the engineering award was found. Retained as a cross-check on the disclosed plate, not as the plate itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Project utilisation in the terminal year</t>
         </is>
       </c>
-      <c r="B116" s="6" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C116" s="15" t="n">
+      <c r="C132" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>Project utilisation in the terminal year, central case</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="14" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project utilisation in the terminal year, central case</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>Nitrate price</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>US$/tonne</t>
         </is>
       </c>
-      <c r="C117" s="13" t="n">
+      <c r="C133" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>Mid-cycle ammonium nitrate pricing</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="14" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
+    <row r="134" ht="14" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>Project cash margin</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>% of revenue</t>
         </is>
       </c>
-      <c r="C118" s="15" t="n">
+      <c r="C134" s="15" t="n">
         <v>0.32</v>
       </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>Conversion margin on ammonium nitrate over its own ammonia feedstock</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="14" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: conversion margin on ammonium nitrate over its own ammonia feedstock</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>Days sales outstanding</t>
         </is>
       </c>
-      <c r="B119" s="6" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C119" s="21" t="n">
+      <c r="C135" s="20" t="n">
         <v>26.77469536556713</v>
       </c>
-      <c r="D119" s="9" t="inlineStr">
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>Constructed: FY2024/25 receivables over revenue</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>Days inventory outstanding</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C120" s="21" t="n">
+      <c r="C136" s="20" t="n">
         <v>165.2475279747788</v>
       </c>
-      <c r="D120" s="9" t="inlineStr">
+      <c r="D136" s="9" t="inlineStr">
         <is>
           <t>Constructed: FY2024/25 inventory over cost of sales</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="14" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Days payable outstanding</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C121" s="21" t="n">
+      <c r="C137" s="20" t="n">
         <v>83.17161071710899</v>
       </c>
-      <c r="D121" s="9" t="inlineStr">
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>Constructed: FY2024/25 payables over cost of sales</t>
         </is>
@@ -6515,23 +6832,23 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>'Assumptions'!C6*'Assumptions'!C9</f>
+        <f>'Assumptions'!C13*'Assumptions'!C16</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>'Assumptions'!C6*'Assumptions'!C10</f>
+        <f>'Assumptions'!C13*'Assumptions'!C17</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>'Assumptions'!C6*'Assumptions'!C11</f>
+        <f>'Assumptions'!C13*'Assumptions'!C18</f>
         <v/>
       </c>
       <c r="E5" s="14">
-        <f>'Assumptions'!C6*'Assumptions'!C12</f>
+        <f>'Assumptions'!C13*'Assumptions'!C19</f>
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>'Assumptions'!C6*'Assumptions'!C13</f>
+        <f>'Assumptions'!C13*'Assumptions'!C20</f>
         <v/>
       </c>
     </row>
@@ -6542,23 +6859,23 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>MIN(B5*'Assumptions'!C8,'Assumptions'!C7)</f>
+        <f>MIN(B5*'Assumptions'!C15,'Assumptions'!C14)</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>MIN(C5*'Assumptions'!C8,'Assumptions'!C7)</f>
+        <f>MIN(C5*'Assumptions'!C15,'Assumptions'!C14)</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>MIN(D5*'Assumptions'!C8,'Assumptions'!C7)</f>
+        <f>MIN(D5*'Assumptions'!C15,'Assumptions'!C14)</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>MIN(E5*'Assumptions'!C8,'Assumptions'!C7)</f>
+        <f>MIN(E5*'Assumptions'!C15,'Assumptions'!C14)</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>MIN(F5*'Assumptions'!C8,'Assumptions'!C7)</f>
+        <f>MIN(F5*'Assumptions'!C15,'Assumptions'!C14)</f>
         <v/>
       </c>
     </row>
@@ -6569,23 +6886,23 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>'Assumptions'!C14</f>
+        <f>'Assumptions'!C21</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>'Assumptions'!C15</f>
+        <f>'Assumptions'!C22</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>'Assumptions'!C16</f>
+        <f>'Assumptions'!C23</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>'Assumptions'!C17</f>
+        <f>'Assumptions'!C24</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>'Assumptions'!C18</f>
+        <f>'Assumptions'!C25</f>
         <v/>
       </c>
     </row>
@@ -6596,23 +6913,23 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>'Assumptions'!C19</f>
+        <f>'Assumptions'!C26</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>'Assumptions'!C20</f>
+        <f>'Assumptions'!C27</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>'Assumptions'!C21</f>
+        <f>'Assumptions'!C28</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>'Assumptions'!C22</f>
+        <f>'Assumptions'!C29</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>'Assumptions'!C23</f>
+        <f>'Assumptions'!C30</f>
         <v/>
       </c>
     </row>
@@ -6650,23 +6967,23 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>'Assumptions'!C26*'Assumptions'!C31*(1-'Assumptions'!C36)</f>
+        <f>'Assumptions'!C33*'Assumptions'!C38*(1-'Assumptions'!C43)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>'Assumptions'!C27*'Assumptions'!C32*(1-'Assumptions'!C36)</f>
+        <f>'Assumptions'!C34*'Assumptions'!C39*(1-'Assumptions'!C43)</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>'Assumptions'!C28*'Assumptions'!C33*(1-'Assumptions'!C36)</f>
+        <f>'Assumptions'!C35*'Assumptions'!C40*(1-'Assumptions'!C43)</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>'Assumptions'!C29*'Assumptions'!C34*(1-'Assumptions'!C36)</f>
+        <f>'Assumptions'!C36*'Assumptions'!C41*(1-'Assumptions'!C43)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>'Assumptions'!C30*'Assumptions'!C35*(1-'Assumptions'!C36)</f>
+        <f>'Assumptions'!C37*'Assumptions'!C42*(1-'Assumptions'!C43)</f>
         <v/>
       </c>
     </row>
@@ -6677,23 +6994,23 @@
         </is>
       </c>
       <c r="B11" s="14">
-        <f>'Assumptions'!C26*'Assumptions'!C31*'Assumptions'!C42</f>
+        <f>'Assumptions'!C33*'Assumptions'!C38*'Assumptions'!C49</f>
         <v/>
       </c>
       <c r="C11" s="14">
-        <f>'Assumptions'!C27*'Assumptions'!C32*'Assumptions'!C42</f>
+        <f>'Assumptions'!C34*'Assumptions'!C39*'Assumptions'!C49</f>
         <v/>
       </c>
       <c r="D11" s="14">
-        <f>'Assumptions'!C28*'Assumptions'!C33*'Assumptions'!C42</f>
+        <f>'Assumptions'!C35*'Assumptions'!C40*'Assumptions'!C49</f>
         <v/>
       </c>
       <c r="E11" s="14">
-        <f>'Assumptions'!C29*'Assumptions'!C34*'Assumptions'!C42</f>
+        <f>'Assumptions'!C36*'Assumptions'!C41*'Assumptions'!C49</f>
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>'Assumptions'!C30*'Assumptions'!C35*'Assumptions'!C42</f>
+        <f>'Assumptions'!C37*'Assumptions'!C42*'Assumptions'!C49</f>
         <v/>
       </c>
     </row>
@@ -6704,23 +7021,23 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>'Assumptions'!C48*'Assumptions'!C31/49.0</f>
+        <f>'Assumptions'!C55*'Assumptions'!C38/'Assumptions'!C8</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>'Assumptions'!C48*'Assumptions'!C32/49.0</f>
+        <f>'Assumptions'!C55*'Assumptions'!C39/'Assumptions'!C8</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>'Assumptions'!C48*'Assumptions'!C33/49.0</f>
+        <f>'Assumptions'!C55*'Assumptions'!C40/'Assumptions'!C8</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>'Assumptions'!C48*'Assumptions'!C34/49.0</f>
+        <f>'Assumptions'!C55*'Assumptions'!C41/'Assumptions'!C8</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>'Assumptions'!C48*'Assumptions'!C35/49.0</f>
+        <f>'Assumptions'!C55*'Assumptions'!C42/'Assumptions'!C8</f>
         <v/>
       </c>
     </row>
@@ -6758,23 +7075,23 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>B7*'Assumptions'!C37/1000000</f>
+        <f>B7*'Assumptions'!C44/1000000</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>C7*'Assumptions'!C38/1000000</f>
+        <f>C7*'Assumptions'!C45/1000000</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>D7*'Assumptions'!C39/1000000</f>
+        <f>D7*'Assumptions'!C46/1000000</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>E7*'Assumptions'!C40/1000000</f>
+        <f>E7*'Assumptions'!C47/1000000</f>
         <v/>
       </c>
       <c r="F14" s="14">
-        <f>F7*'Assumptions'!C41/1000000</f>
+        <f>F7*'Assumptions'!C48/1000000</f>
         <v/>
       </c>
     </row>
@@ -6812,23 +7129,23 @@
         </is>
       </c>
       <c r="B16" s="14">
-        <f>'Assumptions'!C43*B12/1000000</f>
+        <f>'Assumptions'!C50*B12/1000000</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>'Assumptions'!C44*C12/1000000</f>
+        <f>'Assumptions'!C51*C12/1000000</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>'Assumptions'!C45*D12/1000000</f>
+        <f>'Assumptions'!C52*D12/1000000</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>'Assumptions'!C46*E12/1000000</f>
+        <f>'Assumptions'!C53*E12/1000000</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>'Assumptions'!C47*F12/1000000</f>
+        <f>'Assumptions'!C54*F12/1000000</f>
         <v/>
       </c>
     </row>
@@ -6839,23 +7156,23 @@
         </is>
       </c>
       <c r="B17" s="14">
-        <f>'Assumptions'!C49</f>
+        <f>'Assumptions'!C56</f>
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>'Assumptions'!C50</f>
+        <f>'Assumptions'!C57</f>
         <v/>
       </c>
       <c r="D17" s="14">
-        <f>'Assumptions'!C51</f>
+        <f>'Assumptions'!C58</f>
         <v/>
       </c>
       <c r="E17" s="14">
-        <f>'Assumptions'!C52</f>
+        <f>'Assumptions'!C59</f>
         <v/>
       </c>
       <c r="F17" s="14">
-        <f>'Assumptions'!C53</f>
+        <f>'Assumptions'!C60</f>
         <v/>
       </c>
     </row>
@@ -6893,23 +7210,23 @@
         </is>
       </c>
       <c r="B19" s="11">
-        <f>'Assumptions'!C57*'Assumptions'!C58*'Assumptions'!C31</f>
+        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C38</f>
         <v/>
       </c>
       <c r="C19" s="11">
-        <f>'Assumptions'!C57*'Assumptions'!C58*'Assumptions'!C32</f>
+        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C39</f>
         <v/>
       </c>
       <c r="D19" s="11">
-        <f>'Assumptions'!C57*'Assumptions'!C58*'Assumptions'!C33</f>
+        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C40</f>
         <v/>
       </c>
       <c r="E19" s="11">
-        <f>'Assumptions'!C57*'Assumptions'!C58*'Assumptions'!C34</f>
+        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="F19" s="11">
-        <f>'Assumptions'!C57*'Assumptions'!C58*'Assumptions'!C35</f>
+        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C42</f>
         <v/>
       </c>
     </row>
@@ -6920,23 +7237,23 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>B6*'Assumptions'!C56*B19/1000000</f>
+        <f>B6*'Assumptions'!C63*B19/1000000</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>C6*'Assumptions'!C56*C19/1000000</f>
+        <f>C6*'Assumptions'!C63*C19/1000000</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>D6*'Assumptions'!C56*D19/1000000</f>
+        <f>D6*'Assumptions'!C63*D19/1000000</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>E6*'Assumptions'!C56*E19/1000000</f>
+        <f>E6*'Assumptions'!C63*E19/1000000</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>F6*'Assumptions'!C56*F19/1000000</f>
+        <f>F6*'Assumptions'!C63*F19/1000000</f>
         <v/>
       </c>
     </row>
@@ -6947,23 +7264,23 @@
         </is>
       </c>
       <c r="B21" s="19">
-        <f>(1+'Assumptions'!C70)</f>
+        <f>(1+'Assumptions'!C77)</f>
         <v/>
       </c>
       <c r="C21" s="19">
-        <f>(1+'Assumptions'!C70)*(1+'Assumptions'!C71)</f>
+        <f>(1+'Assumptions'!C77)*(1+'Assumptions'!C78)</f>
         <v/>
       </c>
       <c r="D21" s="19">
-        <f>(1+'Assumptions'!C70)*(1+'Assumptions'!C71)*(1+'Assumptions'!C72)</f>
+        <f>(1+'Assumptions'!C77)*(1+'Assumptions'!C78)*(1+'Assumptions'!C79)</f>
         <v/>
       </c>
       <c r="E21" s="19">
-        <f>(1+'Assumptions'!C70)*(1+'Assumptions'!C71)*(1+'Assumptions'!C72)*(1+'Assumptions'!C73)</f>
+        <f>(1+'Assumptions'!C77)*(1+'Assumptions'!C78)*(1+'Assumptions'!C79)*(1+'Assumptions'!C80)</f>
         <v/>
       </c>
       <c r="F21" s="19">
-        <f>(1+'Assumptions'!C70)*(1+'Assumptions'!C71)*(1+'Assumptions'!C72)*(1+'Assumptions'!C73)*(1+'Assumptions'!C74)</f>
+        <f>(1+'Assumptions'!C77)*(1+'Assumptions'!C78)*(1+'Assumptions'!C79)*(1+'Assumptions'!C80)*(1+'Assumptions'!C81)</f>
         <v/>
       </c>
     </row>
@@ -6974,23 +7291,23 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>B5*'Assumptions'!C59*B21/1000000</f>
+        <f>B5*'Assumptions'!C66*B21/1000000</f>
         <v/>
       </c>
       <c r="C22" s="14">
-        <f>C5*'Assumptions'!C59*C21/1000000</f>
+        <f>C5*'Assumptions'!C66*C21/1000000</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>D5*'Assumptions'!C59*D21/1000000</f>
+        <f>D5*'Assumptions'!C66*D21/1000000</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>E5*'Assumptions'!C59*E21/1000000</f>
+        <f>E5*'Assumptions'!C66*E21/1000000</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>F5*'Assumptions'!C59*F21/1000000</f>
+        <f>F5*'Assumptions'!C66*F21/1000000</f>
         <v/>
       </c>
     </row>
@@ -7001,23 +7318,23 @@
         </is>
       </c>
       <c r="B23" s="14">
-        <f>'Assumptions'!C60*B21</f>
+        <f>'Assumptions'!C67*B21</f>
         <v/>
       </c>
       <c r="C23" s="14">
-        <f>'Assumptions'!C60*C21</f>
+        <f>'Assumptions'!C67*C21</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>'Assumptions'!C60*D21</f>
+        <f>'Assumptions'!C67*D21</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>'Assumptions'!C60*E21</f>
+        <f>'Assumptions'!C67*E21</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>'Assumptions'!C60*F21</f>
+        <f>'Assumptions'!C67*F21</f>
         <v/>
       </c>
     </row>
@@ -7028,23 +7345,23 @@
         </is>
       </c>
       <c r="B24" s="14">
-        <f>'Assumptions'!C61*B21</f>
+        <f>'Assumptions'!C68*B21</f>
         <v/>
       </c>
       <c r="C24" s="14">
-        <f>'Assumptions'!C61*C21</f>
+        <f>'Assumptions'!C68*C21</f>
         <v/>
       </c>
       <c r="D24" s="14">
-        <f>'Assumptions'!C61*D21</f>
+        <f>'Assumptions'!C68*D21</f>
         <v/>
       </c>
       <c r="E24" s="14">
-        <f>'Assumptions'!C61*E21</f>
+        <f>'Assumptions'!C68*E21</f>
         <v/>
       </c>
       <c r="F24" s="14">
-        <f>'Assumptions'!C61*F21</f>
+        <f>'Assumptions'!C68*F21</f>
         <v/>
       </c>
     </row>
@@ -7055,23 +7372,23 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>'Assumptions'!C106*(1+0.02*0)+'Assumptions'!C107</f>
+        <f>'Assumptions'!C113*(1+'Assumptions'!C120*0)+'Assumptions'!C114</f>
         <v/>
       </c>
       <c r="C25" s="14">
-        <f>'Assumptions'!C106*(1+0.02*1)+'Assumptions'!C107</f>
+        <f>'Assumptions'!C113*(1+'Assumptions'!C120*1)+'Assumptions'!C114+SUM('Assumptions'!C115:C115)*'Assumptions'!C121</f>
         <v/>
       </c>
       <c r="D25" s="14">
-        <f>'Assumptions'!C106*(1+0.02*2)+'Assumptions'!C107</f>
+        <f>'Assumptions'!C113*(1+'Assumptions'!C120*2)+'Assumptions'!C114+SUM('Assumptions'!C115:C116)*'Assumptions'!C121</f>
         <v/>
       </c>
       <c r="E25" s="14">
-        <f>'Assumptions'!C106*(1+0.02*3)+'Assumptions'!C107</f>
+        <f>'Assumptions'!C113*(1+'Assumptions'!C120*3)+'Assumptions'!C114+SUM('Assumptions'!C115:C117)*'Assumptions'!C121</f>
         <v/>
       </c>
       <c r="F25" s="14">
-        <f>'Assumptions'!C106*(1+0.02*4)+'Assumptions'!C107</f>
+        <f>'Assumptions'!C113*(1+'Assumptions'!C120*4)+'Assumptions'!C114+SUM('Assumptions'!C115:C118)*'Assumptions'!C121</f>
         <v/>
       </c>
     </row>
@@ -7163,23 +7480,23 @@
         </is>
       </c>
       <c r="B29" s="14">
-        <f>B9*'Assumptions'!C62*B21/1000000</f>
+        <f>B9*'Assumptions'!C69*B21/1000000</f>
         <v/>
       </c>
       <c r="C29" s="14">
-        <f>C9*'Assumptions'!C62*C21/1000000</f>
+        <f>C9*'Assumptions'!C69*C21/1000000</f>
         <v/>
       </c>
       <c r="D29" s="14">
-        <f>D9*'Assumptions'!C62*D21/1000000</f>
+        <f>D9*'Assumptions'!C69*D21/1000000</f>
         <v/>
       </c>
       <c r="E29" s="14">
-        <f>E9*'Assumptions'!C62*E21/1000000</f>
+        <f>E9*'Assumptions'!C69*E21/1000000</f>
         <v/>
       </c>
       <c r="F29" s="14">
-        <f>F9*'Assumptions'!C62*F21/1000000</f>
+        <f>F9*'Assumptions'!C69*F21/1000000</f>
         <v/>
       </c>
     </row>
@@ -7190,23 +7507,23 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>'Assumptions'!C63*B21</f>
+        <f>'Assumptions'!C70*B21</f>
         <v/>
       </c>
       <c r="C30" s="14">
-        <f>'Assumptions'!C63*C21</f>
+        <f>'Assumptions'!C70*C21</f>
         <v/>
       </c>
       <c r="D30" s="14">
-        <f>'Assumptions'!C63*D21</f>
+        <f>'Assumptions'!C70*D21</f>
         <v/>
       </c>
       <c r="E30" s="14">
-        <f>'Assumptions'!C63*E21</f>
+        <f>'Assumptions'!C70*E21</f>
         <v/>
       </c>
       <c r="F30" s="14">
-        <f>'Assumptions'!C63*F21</f>
+        <f>'Assumptions'!C70*F21</f>
         <v/>
       </c>
     </row>
@@ -7217,23 +7534,23 @@
         </is>
       </c>
       <c r="B31" s="14">
-        <f>'Assumptions'!C64*B21</f>
+        <f>'Assumptions'!C71*B21</f>
         <v/>
       </c>
       <c r="C31" s="14">
-        <f>'Assumptions'!C64*C21</f>
+        <f>'Assumptions'!C71*C21</f>
         <v/>
       </c>
       <c r="D31" s="14">
-        <f>'Assumptions'!C64*D21</f>
+        <f>'Assumptions'!C71*D21</f>
         <v/>
       </c>
       <c r="E31" s="14">
-        <f>'Assumptions'!C64*E21</f>
+        <f>'Assumptions'!C71*E21</f>
         <v/>
       </c>
       <c r="F31" s="14">
-        <f>'Assumptions'!C64*F21</f>
+        <f>'Assumptions'!C71*F21</f>
         <v/>
       </c>
     </row>
@@ -7244,23 +7561,23 @@
         </is>
       </c>
       <c r="B32" s="14">
-        <f>'Assumptions'!C65</f>
+        <f>'Assumptions'!C72</f>
         <v/>
       </c>
       <c r="C32" s="14">
-        <f>'Assumptions'!C66</f>
+        <f>'Assumptions'!C73</f>
         <v/>
       </c>
       <c r="D32" s="14">
-        <f>'Assumptions'!C67</f>
+        <f>'Assumptions'!C74</f>
         <v/>
       </c>
       <c r="E32" s="14">
-        <f>'Assumptions'!C68</f>
+        <f>'Assumptions'!C75</f>
         <v/>
       </c>
       <c r="F32" s="14">
-        <f>'Assumptions'!C69</f>
+        <f>'Assumptions'!C76</f>
         <v/>
       </c>
     </row>
@@ -7424,7 +7741,7 @@
           <t>Egyptian industrial range, low</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="20" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -7439,7 +7756,7 @@
           <t>Egyptian industrial range, high</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="20" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -7511,7 +7828,7 @@
         </is>
       </c>
       <c r="B12" s="11">
-        <f>(B9+B10+B11)*1000000/1986578999</f>
+        <f>(B9+B10+B11)*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr"/>
@@ -7523,7 +7840,7 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>(B5*B6+B10+B11)*1000000/1986578999</f>
+        <f>(B5*B6+B10+B11)*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C13" s="9" t="inlineStr"/>
@@ -7535,7 +7852,7 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>(B5*B7+B10+B11)*1000000/1986578999</f>
+        <f>(B5*B7+B10+B11)*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr"/>
@@ -7614,7 +7931,7 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>B21-155000-40000</f>
+        <f>B21-'Assumptions'!C21-'Assumptions'!C26</f>
         <v/>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -7660,7 +7977,7 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>B22*B23*B24*(1-'Assumptions'!C36)/1000000</f>
+        <f>B22*B23*B24*(1-'Assumptions'!C43)/1000000</f>
         <v/>
       </c>
       <c r="C25" s="9" t="inlineStr"/>
@@ -7726,7 +8043,7 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>(B29-890.591)*(1-'Assumptions'!C92)</f>
+        <f>(B29-'Assumptions'!C113-'Assumptions'!C114)*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -7738,11 +8055,11 @@
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Value per share at ten times (EGP)</t>
+          <t>Value per share at the central multiple (EGP)</t>
         </is>
       </c>
       <c r="B31" s="11">
-        <f>(B30*10+B10+B11)*1000000/1986578999</f>
+        <f>(B30*'Assumptions'!C10+B10+B11)*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -7754,11 +8071,11 @@
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>At eight times (EGP)</t>
+          <t>At the low multiple (EGP)</t>
         </is>
       </c>
       <c r="B32" s="11">
-        <f>(B30*8+B10+B11)*1000000/1986578999</f>
+        <f>(B30*'Assumptions'!C9+B10+B11)*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C32" s="9" t="inlineStr"/>
@@ -7766,11 +8083,11 @@
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>At twelve times (EGP)</t>
+          <t>At the high multiple (EGP)</t>
         </is>
       </c>
       <c r="B33" s="11">
-        <f>(B30*12+B10+B11)*1000000/1986578999</f>
+        <f>(B30*'Assumptions'!C11+B10+B11)*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="C33" s="9" t="inlineStr"/>
@@ -7786,15 +8103,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
@@ -8008,23 +8325,23 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>B9*(1-'Assumptions'!C92)</f>
+        <f>B9*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>C9*(1-'Assumptions'!C92)</f>
+        <f>C9*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>D9*(1-'Assumptions'!C92)</f>
+        <f>D9*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>E9*(1-'Assumptions'!C92)</f>
+        <f>E9*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>F9*(1-'Assumptions'!C92)</f>
+        <f>F9*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
     </row>
@@ -8062,23 +8379,23 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>-($I$5*'Assumptions'!C108+$I$6*(1-$I$5)+B5*'Assumptions'!C113)</f>
+        <f>-($I$5*'Assumptions'!C115+$I$6*(1-$I$5)+B5*'Assumptions'!C127)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>-($I$5*'Assumptions'!C109+C5*'Assumptions'!C113)</f>
+        <f>-($I$5*'Assumptions'!C116+C5*'Assumptions'!C127)</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>-($I$5*'Assumptions'!C110+D5*'Assumptions'!C113)</f>
+        <f>-($I$5*'Assumptions'!C117+D5*'Assumptions'!C127)</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>-($I$5*'Assumptions'!C111+E5*'Assumptions'!C113)</f>
+        <f>-($I$5*'Assumptions'!C118+E5*'Assumptions'!C127)</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>-($I$5*'Assumptions'!C112+F5*'Assumptions'!C113)</f>
+        <f>-($I$5*'Assumptions'!C119+F5*'Assumptions'!C127)</f>
         <v/>
       </c>
     </row>
@@ -8143,23 +8460,23 @@
         </is>
       </c>
       <c r="B15" s="27">
-        <f>'Assumptions'!C95+('Assumptions'!C101-'Assumptions'!C95)*0/5</f>
+        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*0/5</f>
         <v/>
       </c>
       <c r="C15" s="27">
-        <f>'Assumptions'!C95+('Assumptions'!C101-'Assumptions'!C95)*1/5</f>
+        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*1/5</f>
         <v/>
       </c>
       <c r="D15" s="27">
-        <f>'Assumptions'!C95+('Assumptions'!C101-'Assumptions'!C95)*2/5</f>
+        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*2/5</f>
         <v/>
       </c>
       <c r="E15" s="27">
-        <f>'Assumptions'!C95+('Assumptions'!C101-'Assumptions'!C95)*3/5</f>
+        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*3/5</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>'Assumptions'!C95+('Assumptions'!C101-'Assumptions'!C95)*4/5</f>
+        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*4/5</f>
         <v/>
       </c>
     </row>
@@ -8245,11 +8562,11 @@
         </is>
       </c>
       <c r="B21" s="14">
-        <f>F9*(1+'Assumptions'!C102)</f>
+        <f>F9*(1+'Assumptions'!C109)</f>
         <v/>
       </c>
       <c r="D21" s="14">
-        <f>F9*(1+'Assumptions'!C102)</f>
+        <f>(F9+SUM('Assumptions'!C115:C118)*'Assumptions'!C121)*(1+'Assumptions'!C109)</f>
         <v/>
       </c>
     </row>
@@ -8260,26 +8577,26 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>'Assumptions'!C115*'Assumptions'!C116*'Assumptions'!C117*64.6855/1000000</f>
+        <f>'Assumptions'!C130*'Assumptions'!C132*'Assumptions'!C133*('Assumptions'!C42*(1+'Assumptions'!C109-'Assumptions'!C124))/1000000</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>'Assumptions'!C115*0*'Assumptions'!C117*64.6855/1000000</f>
+        <f>'Assumptions'!C130*0*'Assumptions'!C133*('Assumptions'!C42*(1+'Assumptions'!C109-'Assumptions'!C124))/1000000</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Project operating profit</t>
+          <t>Project operating profit, after its own depreciation</t>
         </is>
       </c>
       <c r="B23" s="14">
-        <f>B22*'Assumptions'!C118</f>
+        <f>B22*'Assumptions'!C134-'Assumptions'!C125*'Assumptions'!C126*'Assumptions'!C121</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>D22*'Assumptions'!C118</f>
+        <f>D22*'Assumptions'!C134-0*'Assumptions'!C126*'Assumptions'!C121</f>
         <v/>
       </c>
     </row>
@@ -8305,11 +8622,11 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>B24*(1-'Assumptions'!C92)</f>
+        <f>B24*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
       <c r="D25" s="14">
-        <f>D24*(1-'Assumptions'!C92)</f>
+        <f>D24*(1-'Assumptions'!C99)</f>
         <v/>
       </c>
     </row>
@@ -8320,11 +8637,11 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>'Assumptions'!C102/'Assumptions'!C103</f>
+        <f>'Assumptions'!C109/'Assumptions'!C110</f>
         <v/>
       </c>
       <c r="D26" s="8">
-        <f>'Assumptions'!C102/'Assumptions'!C103</f>
+        <f>'Assumptions'!C109/'Assumptions'!C110</f>
         <v/>
       </c>
     </row>
@@ -8350,11 +8667,11 @@
         </is>
       </c>
       <c r="B28" s="14">
-        <f>B27*(1+'Assumptions'!C102)/('Assumptions'!C101-'Assumptions'!C102)</f>
+        <f>B27/('Assumptions'!C108-'Assumptions'!C109)</f>
         <v/>
       </c>
       <c r="D28" s="14">
-        <f>D27*(1+'Assumptions'!C102)/('Assumptions'!C101-'Assumptions'!C102)</f>
+        <f>D27/('Assumptions'!C108-'Assumptions'!C109)</f>
         <v/>
       </c>
     </row>
@@ -8384,7 +8701,7 @@
         <v/>
       </c>
       <c r="D36" s="14">
-        <f>SUM(B17:F17)+7259.375005</f>
+        <f>SUM(B54:F54)</f>
         <v/>
       </c>
     </row>
@@ -8488,11 +8805,11 @@
         </is>
       </c>
       <c r="B44" s="11">
-        <f>B45*1000000/1986578999</f>
+        <f>B45*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
       <c r="D44" s="11">
-        <f>D45*1000000/1986578999</f>
+        <f>D45*1000000/'Assumptions'!C6</f>
         <v/>
       </c>
     </row>
@@ -8508,6 +8825,207 @@
       </c>
       <c r="D45" s="14">
         <f>D37-D41+D42+D43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>PROGRAMME STOPPED — the same operating build, project capital removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>EGP million</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>FY2026/27</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>FY2027/28</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>FY2028/29</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>FY2029/30</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>FY2030/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Free cash flow, programme carried through</t>
+        </is>
+      </c>
+      <c r="B49" s="14">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C49" s="14">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="D49" s="14">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="E49" s="14">
+        <f>E14</f>
+        <v/>
+      </c>
+      <c r="F49" s="14">
+        <f>F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Add back project capital not spent</t>
+        </is>
+      </c>
+      <c r="B50" s="14">
+        <f>+'Assumptions'!C115</f>
+        <v/>
+      </c>
+      <c r="C50" s="14">
+        <f>+'Assumptions'!C116</f>
+        <v/>
+      </c>
+      <c r="D50" s="14">
+        <f>+'Assumptions'!C117</f>
+        <v/>
+      </c>
+      <c r="E50" s="14">
+        <f>+'Assumptions'!C118</f>
+        <v/>
+      </c>
+      <c r="F50" s="14">
+        <f>+'Assumptions'!C119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Less the wind-down cost</t>
+        </is>
+      </c>
+      <c r="B51" s="14">
+        <f>-'Assumptions'!C128</f>
+        <v/>
+      </c>
+      <c r="C51" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D51" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E51" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F51" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Less the tax shield on depreciation never incurred</t>
+        </is>
+      </c>
+      <c r="B52" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C52" s="14">
+        <f>-SUM('Assumptions'!C115:C115)*'Assumptions'!C121*'Assumptions'!C99</f>
+        <v/>
+      </c>
+      <c r="D52" s="14">
+        <f>-SUM('Assumptions'!C115:C116)*'Assumptions'!C121*'Assumptions'!C99</f>
+        <v/>
+      </c>
+      <c r="E52" s="14">
+        <f>-SUM('Assumptions'!C115:C117)*'Assumptions'!C121*'Assumptions'!C99</f>
+        <v/>
+      </c>
+      <c r="F52" s="14">
+        <f>-SUM('Assumptions'!C115:C118)*'Assumptions'!C121*'Assumptions'!C99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>FREE CASH FLOW, PROGRAMME STOPPED</t>
+        </is>
+      </c>
+      <c r="B53" s="14">
+        <f>B49+B50+B51+B52</f>
+        <v/>
+      </c>
+      <c r="C53" s="14">
+        <f>C49+C50+C51+C52</f>
+        <v/>
+      </c>
+      <c r="D53" s="14">
+        <f>D49+D50+D51+D52</f>
+        <v/>
+      </c>
+      <c r="E53" s="14">
+        <f>E49+E50+E51+E52</f>
+        <v/>
+      </c>
+      <c r="F53" s="14">
+        <f>F49+F50+F51+F52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Present value</t>
+        </is>
+      </c>
+      <c r="B54" s="14">
+        <f>B53*B16</f>
+        <v/>
+      </c>
+      <c r="C54" s="14">
+        <f>C53*C16</f>
+        <v/>
+      </c>
+      <c r="D54" s="14">
+        <f>D53*D16</f>
+        <v/>
+      </c>
+      <c r="E54" s="14">
+        <f>E53*E16</f>
+        <v/>
+      </c>
+      <c r="F54" s="14">
+        <f>F53*F16</f>
         <v/>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_08082026.xlsx
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>7.340407384570012</v>
+        <v>15.4744443192992</v>
       </c>
     </row>
     <row r="27">
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
